--- a/ResourcesPH/configPH.xlsx
+++ b/ResourcesPH/configPH.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="118">
   <si>
     <t>screenName</t>
   </si>
@@ -380,12 +380,6 @@
   </si>
   <si>
     <t>001001</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
 </sst>
 </file>
@@ -819,7 +813,7 @@
         <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
@@ -839,7 +833,7 @@
         <v>90</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -859,7 +853,7 @@
         <v>69</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -876,7 +870,7 @@
         <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -896,7 +890,7 @@
         <v>70</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -916,7 +910,7 @@
         <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -936,7 +930,7 @@
         <v>75</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -956,7 +950,7 @@
         <v>79</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -976,7 +970,7 @@
         <v>82</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -996,7 +990,7 @@
         <v>85</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1016,7 +1010,7 @@
         <v>87</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1171,7 +1165,7 @@
       </c>
       <c r="D7" s="4" t="str">
         <f ca="1" xml:space="preserve"> TEXT(TODAY() - 6, "yyyy-mm-dd")</f>
-        <v>2025-10-23</v>
+        <v>2025-10-31</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1186,7 +1180,7 @@
       </c>
       <c r="D8" s="5" t="str">
         <f ca="1">TEXT(TODAY(), "yyyy-mm-dd")</f>
-        <v>2025-10-29</v>
+        <v>2025-11-06</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
